--- a/AtchisonRegime/Outputs/Brazil/df_regSTRates_Brazil.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/df_regSTRates_Brazil.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H341"/>
+  <dimension ref="A1:H342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9316,6 +9316,32 @@
         <v>1</v>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2.34677</v>
+      </c>
+      <c r="C342" t="n">
+        <v>2.406163333333333</v>
+      </c>
+      <c r="D342" t="n">
+        <v>2.779883820833333</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1.273754370801845</v>
+      </c>
+      <c r="F342" t="b">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>-0.2934007498358872</v>
+      </c>
+      <c r="H342" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
